--- a/docs/test/unit/NOUS-97/観点表_settings.xlsx
+++ b/docs/test/unit/NOUS-97/観点表_settings.xlsx
@@ -13,9 +13,9 @@
     <sheet name="対象概要" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'観点表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>B18-T, B19-F</t>
+          <t>B18-F, B19-F</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -3171,55 +3171,55 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-055</t>
+          <t>TC-UT_WLD-066</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/api/world</t>
+          <t>updateSettings</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>分岐網羅</t>
+          <t>状態遷移</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>世界がないときに 2 回呼んでも、作る世界は 1 つだけ</t>
+          <t>running で新しい上限を超えたときは、設定の更新と同じ処理の中で running → limit_stopped にする</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>前提：世界なし
-入力：GET を 2 回（順に）</t>
+          <t>前提：running、実行回数 50。worldService.enterLimitStopped は何もしない差し替え
+入力：dailyRunsLimit 50</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>どちらも 200 で同じ worldId、worlds は 1 行</t>
+          <t>stateChanged running→limit_stopped、worlds は limit_stopped・runs_limit・running_since null</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>B21-T, B21-F</t>
+          <t>B16-T</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
+          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）、recordAudit は実物（admin_audit_logs）、enterLimitStopped を vi.fn に差し替え</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-055 世界がないときに GET /world を2回呼んでも、作る世界は1つだけ</t>
+          <t>TC-UT_WLD-066 running で新しい上限を超えたときは、設定の更新と同じ処理の中で running → limit_stopped にする</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -3231,8 +3231,9 @@
       <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：一部 TC-NOUS58_DEV-13（1 回だけ）
-同時に届くときは確認事項 2</t>
+          <t>既存テスト：一部 TC-NOUS58_DEV-12（enterLimitStopped の実物を使うため、トランザクションの分かれ目は見ていない）
+疑い：実装は enterLimitStopped（コミットの後の別トランザクション）に任せるため、差し替えると running のまま。疑い 1
+world.md 6章 トランザクション制御の表</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3243,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-056</t>
+          <t>TC-UT_WLD-067</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3252,33 +3253,33 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>同値分割</t>
+          <t>エラー処理</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
+          <t>世界がないときに GET が同時に2つ届いても、どちらも 200 で、作る世界は1つだけ</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>前提：準備中、上限 5,000・200、daily_usage なし
-入力：GET</t>
+          <t>前提：世界なし
+入力：GET を Promise.all で2つ同時に</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>usage { 2026-10-22, 0, 0, 5000, 200, freeTierNeurons 10000 }</t>
+          <t>どちらも 200、worlds は 1 行</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>B21-F</t>
+          <t>B21-T</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3290,7 +3291,7 @@
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-056 利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
+          <t>TC-UT_WLD-067 世界がないときに GET /world が同時に2つ届いても、どちらも 200 で、作る世界は1つだけ</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -3302,7 +3303,9 @@
       <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：一部 TC-NOUS58_DEV-14（利用量があり既定の上限のとき）</t>
+          <t>既存テスト：一部 TC-UT_WLD-055（順に2回だけ）
+疑い：find と create の間で割り込まれると 2つ目が 500 になりうる。疑い 2
+1つのプロセスの中では同期の処理のため割り込まれない見込み</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3315,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-057</t>
+          <t>TC-UT_WLD-055</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3327,28 +3330,28 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>同値分割</t>
+          <t>分岐網羅</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>一時停止中は、時間が進んでも worldTimeSec が増えない</t>
+          <t>世界がないときに 2 回呼んでも、作る世界は 1 つだけ</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>前提：start → 30 秒 → pause → 1 時間
-入力：GET</t>
+          <t>前提：世界なし
+入力：GET を 2 回（順に）</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>state paused、worldTimeSec 30</t>
+          <t>どちらも 200 で同じ worldId、worlds は 1 行</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>B21-F</t>
+          <t>B21-T, B21-F</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -3360,7 +3363,7 @@
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-057 一時停止中は、時間が進んでも worldTimeSec が増えない</t>
+          <t>TC-UT_WLD-055 世界がないときに GET /world を2回呼んでも、作る世界は1つだけ</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -3372,7 +3375,8 @@
       <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし</t>
+          <t>既存テスト：一部 TC-NOUS58_DEV-13（1 回だけ）
+同時に届くときは確認事項 2</t>
         </is>
       </c>
     </row>
@@ -3382,41 +3386,45 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-058</t>
+          <t>TC-UT_WLD-056</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/api/world/start</t>
+          <t>GET /admin/api/world</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>エラー処理</t>
+          <t>同値分割</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>CSRF トークンのない POST は 403 で、世界の状態を変えない</t>
+          <t>利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>前提：準備中、active 1 体
-入力：POST /world/start（Cookie だけ）</t>
+          <t>前提：準備中、上限 5,000・200、daily_usage なし
+入力：GET</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>403 CSRF_INVALID、preparing のまま、監査なし、wake なし</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>usage { 2026-10-22, 0, 0, 5000, 200, freeTierNeurons 10000 }</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>B21-F</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
@@ -3426,7 +3434,7 @@
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-058 CSRF トークンのない POST /world/start は 403 で、世界の状態を変えない</t>
+          <t>TC-UT_WLD-056 利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
@@ -3438,7 +3446,7 @@
       <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし（world の DEV はすべて CSRF あり）</t>
+          <t>既存テスト：一部 TC-NOUS58_DEV-14（利用量があり既定の上限のとき）</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3456,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-059</t>
+          <t>TC-UT_WLD-057</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3458,31 +3466,35 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>異常系</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>エラー処理</t>
+          <t>同値分割</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>ログインしていない GET は 401 ADMIN_UNAUTHORIZED</t>
+          <t>一時停止中は、時間が進んでも worldTimeSec が増えない</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>前提：準備中の世界
-入力：GET（Cookie なし）</t>
+          <t>前提：start → 30 秒 → pause → 1 時間
+入力：GET</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>401 ADMIN_UNAUTHORIZED</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr"/>
+          <t>state paused、worldTimeSec 30</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>B21-F</t>
+        </is>
+      </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
           <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
@@ -3492,7 +3504,7 @@
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-059 ログインしていない GET /world は 401 ADMIN_UNAUTHORIZED</t>
+          <t>TC-UT_WLD-057 一時停止中は、時間が進んでも worldTimeSec が増えない</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -3514,12 +3526,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-060</t>
+          <t>TC-UT_WLD-058</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/api/world/reset</t>
+          <t>POST /admin/api/world/start</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3529,30 +3541,26 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>同値分割</t>
+          <t>エラー処理</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>confirmName のない本文は 400 VALIDATION_ERROR（fields.confirmName）</t>
+          <t>CSRF トークンのない POST は 403 で、世界の状態を変えない</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>前提：準備中の世界
-入力：本文 {}</t>
+          <t>前提：準備中、active 1 体
+入力：POST /world/start（Cookie だけ）</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR、fields.confirmName</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>B20-F, B22-T</t>
-        </is>
-      </c>
+          <t>403 CSRF_INVALID、preparing のまま、監査なし、wake なし</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
@@ -3562,7 +3570,7 @@
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-060 confirmName のない本文の POST /world/reset は 400 VALIDATION_ERROR（fields.confirmName）</t>
+          <t>TC-UT_WLD-058 CSRF トークンのない POST /world/start は 403 で、世界の状態を変えない</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -3574,7 +3582,7 @@
       <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：一部 TC-NOUS58_DEV-18（空文字だけ）</t>
+          <t>既存テスト：なし（world の DEV はすべて CSRF あり）</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3592,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-061</t>
+          <t>TC-UT_WLD-059</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>PUT /admin/api/settings</t>
+          <t>GET /admin/api/world</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3599,30 +3607,26 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>境界値</t>
+          <t>エラー処理</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
+          <t>ログインしていない GET は 401 ADMIN_UNAUTHORIZED</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
           <t>前提：準備中の世界
-入力：9 項目それぞれの min-1・max+1（18 通り、ほかは既定）</t>
+入力：GET（Cookie なし）</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR、fields にその項目、world_settings は変わらない</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>B11-T</t>
-        </is>
-      </c>
+          <t>401 ADMIN_UNAUTHORIZED</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
           <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
@@ -3632,7 +3636,7 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-061 数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
+          <t>TC-UT_WLD-059 ログインしていない GET /world は 401 ADMIN_UNAUTHORIZED</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -3644,7 +3648,7 @@
       <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：一部 TC-NOUS58_DEV-20（cycleMinutes 5 だけ）</t>
+          <t>既存テスト：なし</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3658,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-062</t>
+          <t>TC-UT_WLD-060</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>PUT /admin/api/settings</t>
+          <t>POST /admin/api/world/reset</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3674,23 +3678,23 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>modelId が選択肢の 2 値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
+          <t>confirmName のない本文は 400 VALIDATION_ERROR（fields.confirmName）</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
           <t>前提：準備中の世界
-入力：modelId @cf/meta/llama-3-8b-instruct</t>
+入力：本文 {}</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR、fields.modelId</t>
+          <t>400 VALIDATION_ERROR、fields.confirmName</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>B11-T</t>
+          <t>B20-F, B22-T</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3702,7 +3706,7 @@
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-062 modelId が選択肢の2値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
+          <t>TC-UT_WLD-060 confirmName のない本文の POST /world/reset は 400 VALIDATION_ERROR（fields.confirmName）</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -3714,7 +3718,7 @@
       <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし</t>
+          <t>既存テスト：一部 TC-NOUS58_DEV-18（空文字だけ）</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3728,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-063</t>
+          <t>TC-UT_WLD-061</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3739,23 +3743,23 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>同値分割</t>
+          <t>境界値</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
+          <t>数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
           <t>前提：準備中の世界
-入力：maxConcurrency を抜いた本文</t>
+入力：9 項目それぞれの min-1・max+1（18 通り、ほかは既定）</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR、fields.maxConcurrency</t>
+          <t>400 VALIDATION_ERROR、fields にその項目、world_settings は変わらない</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3772,7 +3776,7 @@
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-063 必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
+          <t>TC-UT_WLD-061 数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -3784,7 +3788,7 @@
       <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし</t>
+          <t>既存テスト：一部 TC-NOUS58_DEV-20（cycleMinutes 5 だけ）</t>
         </is>
       </c>
     </row>
@@ -3794,55 +3798,55 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-064</t>
+          <t>TC-UT_WLD-062</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>GET・PUT /admin/api/settings</t>
+          <t>PUT /admin/api/settings</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>依存</t>
+          <t>同値分割</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>GET はモデルの 2 値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+          <t>modelId が選択肢の 2 値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>前提：configureWorldApi の promptsDir に v1・v2（mkdtemp）
-入力：GET、PUT promptVersion v2</t>
+          <t>前提：準備中の世界
+入力：modelId @cf/meta/llama-3-8b-instruct</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>modelOptions は 2 値、promptVersions [v1, v2]、PUT は 200 で prompt_version v2</t>
+          <t>400 VALIDATION_ERROR、fields.modelId</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>B19-T, B12-F, B9-T</t>
+          <t>B11-T</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）、promptsDir を一時ディレクトリに差し替え</t>
+          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-064 GET /settings はモデルの2値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+          <t>TC-UT_WLD-062 modelId が選択肢の2値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -3854,7 +3858,7 @@
       <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：一部 TC-NOUS58_DEV-19（既定の prompts/ の v1 だけ）</t>
+          <t>既存テスト：なし</t>
         </is>
       </c>
     </row>
@@ -3864,55 +3868,55 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-065</t>
+          <t>TC-UT_WLD-063</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/api/settings</t>
+          <t>PUT /admin/api/settings</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>依存</t>
+          <t>同値分割</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+          <t>必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>前提：参加の確率をすべて 1 にした generationConfig、活動頻度 3 の active 1 体
-入力：GET</t>
+          <t>前提：準備中の世界
+入力：maxConcurrency を抜いた本文</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>activeAgents 1、avgParticipation 1、estimatedDailyRuns 72</t>
+          <t>400 VALIDATION_ERROR、fields.maxConcurrency</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>B18-T</t>
+          <t>B11-T</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）、generationConfig を差し替え</t>
+          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-065 configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+          <t>TC-UT_WLD-063 必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
@@ -3928,9 +3932,149 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-064</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GET・PUT /admin/api/settings</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>依存</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>GET はモデルの 2 値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>前提：configureWorldApi の promptsDir に v1・v2（mkdtemp）
+入力：GET、PUT promptVersion v2</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>modelOptions は 2 値、promptVersions [v1, v2]、PUT は 200 で prompt_version v2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>B19-T, B12-F, B9-T</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）、promptsDir を一時ディレクトリに差し替え</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-064 GET /settings はモデルの2値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr"/>
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：一部 TC-NOUS58_DEV-19（既定の prompts/ の v1 だけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-065</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/api/settings</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>依存</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>前提：参加の確率をすべて 1 にした generationConfig、活動頻度 3 の active 1 体
+入力：GET</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>activeAgents 1、avgParticipation 1、estimatedDailyRuns 72</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>B18-T</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>FakeClock 2026-10-22T00:00:00.000Z、一時 DB（createTestDb）、createAdminApp（requireAdminSession・requireCsrf を通す）、configureWorldApi で SchedulerControl の差し替え（stopAll → 0、wake は vi.fn）、generationConfig を差し替え</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-065 configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr"/>
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：なし</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q51"/>
-  <conditionalFormatting sqref="A5:Q101">
+  <autoFilter ref="A4:Q53"/>
+  <conditionalFormatting sqref="A5:Q103">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N5="NG"</formula>
     </cfRule>
@@ -3942,10 +4086,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N5:N101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常系,異常系"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3997,7 +4141,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTA(観点表!$B$5:$B$101)</f>
+        <f>COUNTA(観点表!$B$5:$B$103)</f>
         <v/>
       </c>
     </row>
@@ -4008,7 +4152,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$101,"正常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$103,"正常系")</f>
         <v/>
       </c>
     </row>
@@ -4019,7 +4163,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$101,"異常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$103,"異常系")</f>
         <v/>
       </c>
     </row>
@@ -4039,7 +4183,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"エラー処理")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"エラー処理")</f>
         <v/>
       </c>
     </row>
@@ -4050,7 +4194,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"依存")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"依存")</f>
         <v/>
       </c>
     </row>
@@ -4061,7 +4205,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"分岐網羅")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"分岐網羅")</f>
         <v/>
       </c>
     </row>
@@ -4072,7 +4216,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"同値分割")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"同値分割")</f>
         <v/>
       </c>
     </row>
@@ -4083,7 +4227,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"境界値")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"境界値")</f>
         <v/>
       </c>
     </row>
@@ -4094,7 +4238,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"状態遷移")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"状態遷移")</f>
         <v/>
       </c>
     </row>
@@ -4105,7 +4249,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$101,"開発者テスト")</f>
+        <f>COUNTIF(観点表!$E$5:$E$103,"開発者テスト")</f>
         <v/>
       </c>
     </row>
@@ -4125,7 +4269,7 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(観点表!$K$5:$K$101,"?*")</f>
+        <f>COUNTIF(観点表!$K$5:$K$103,"?*")</f>
         <v/>
       </c>
     </row>
@@ -4156,7 +4300,7 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$101,"未実施")</f>
+        <f>COUNTIF(観点表!$N$5:$N$103,"未実施")</f>
         <v/>
       </c>
     </row>
@@ -4167,7 +4311,7 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$101,"OK")</f>
+        <f>COUNTIF(観点表!$N$5:$N$103,"OK")</f>
         <v/>
       </c>
     </row>
@@ -4178,7 +4322,7 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$101,"NG")</f>
+        <f>COUNTIF(観点表!$N$5:$N$103,"NG")</f>
         <v/>
       </c>
     </row>
@@ -4189,7 +4333,7 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$101,"保留")</f>
+        <f>COUNTIF(観点表!$N$5:$N$103,"保留")</f>
         <v/>
       </c>
     </row>
@@ -4200,7 +4344,7 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$101,"対象外")</f>
+        <f>COUNTIF(観点表!$N$5:$N$103,"対象外")</f>
         <v/>
       </c>
     </row>
@@ -4237,7 +4381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5017,12 +5161,12 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-055</t>
+          <t>TC-UT_WLD-066</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>世界がないときに 2 回呼んでも、作る世界は 1 つだけ</t>
+          <t>running で新しい上限を超えたときは、設定の更新と同じ処理の中で running → limit_stopped にする</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -5037,12 +5181,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-056</t>
+          <t>TC-UT_WLD-067</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
+          <t>世界がないときに GET が同時に2つ届いても、どちらも 200 で、作る世界は1つだけ</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -5057,12 +5201,12 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-057</t>
+          <t>TC-UT_WLD-055</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>一時停止中は、時間が進んでも worldTimeSec が増えない</t>
+          <t>世界がないときに 2 回呼んでも、作る世界は 1 つだけ</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -5077,12 +5221,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-058</t>
+          <t>TC-UT_WLD-056</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>CSRF トークンのない POST は 403 で、世界の状態を変えない</t>
+          <t>利用日の行がなければ利用量は 0 で、上限はその世界の world_settings の値を返す</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -5097,12 +5241,12 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-059</t>
+          <t>TC-UT_WLD-057</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>ログインしていない GET は 401 ADMIN_UNAUTHORIZED</t>
+          <t>一時停止中は、時間が進んでも worldTimeSec が増えない</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -5117,12 +5261,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-060</t>
+          <t>TC-UT_WLD-058</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>confirmName のない本文は 400 VALIDATION_ERROR（fields.confirmName）</t>
+          <t>CSRF トークンのない POST は 403 で、世界の状態を変えない</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -5137,12 +5281,12 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-061</t>
+          <t>TC-UT_WLD-059</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
+          <t>ログインしていない GET は 401 ADMIN_UNAUTHORIZED</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -5157,12 +5301,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-062</t>
+          <t>TC-UT_WLD-060</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>modelId が選択肢の 2 値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
+          <t>confirmName のない本文は 400 VALIDATION_ERROR（fields.confirmName）</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -5177,12 +5321,12 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-063</t>
+          <t>TC-UT_WLD-061</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
+          <t>数値の項目が下限-1・上限+1 なら 400 VALIDATION_ERROR（fields にその項目）で、設定を変えない</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -5197,12 +5341,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-064</t>
+          <t>TC-UT_WLD-062</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>GET はモデルの 2 値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+          <t>modelId が選択肢の 2 値以外なら 400 VALIDATION_ERROR（fields.modelId）</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -5217,12 +5361,12 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_WLD-065</t>
+          <t>TC-UT_WLD-063</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+          <t>必須の項目が欠けていれば 400 VALIDATION_ERROR（fields にその項目）</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -5234,8 +5378,48 @@
       <c r="E51" s="13" t="inlineStr"/>
       <c r="F51" s="13" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-064</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>GET はモデルの 2 値と、設定した prompts の版の一覧を返し、その版を PUT で保存できる</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr"/>
+      <c r="F52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_WLD-065</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>configureWorldApi で渡した generation の設定（参加の確率）で見込みを計算する</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr"/>
+      <c r="F53" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F51"/>
+  <autoFilter ref="A4:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5735,28 +5919,28 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：PUT /settings で running のまま新しい上限を超えたとき、running → limit_stopped は設定の更新とは別のトランザクション（コミットの後の enterLimitStopped）で行う。world.md 6章のトランザクション制御の表は updateSettings を「world_settings の更新、状態の変更、recordAudit」で1つとしている。NOUS-58 の決めたこと 4 として再鑑で認められているため疑いにはしないが、間に巡が始まる余地がある。設計書の表をどちらに合わせるかの確認</t>
+          <t>・疑い 1：PUT /settings で running のまま新しい上限を超えたとき、running → limit_stopped を設定の更新とは別のトランザクション（コミットの後の enterLimitStopped）で行っている。world.md 6章のトランザクション制御の表のとおり、設定の更新と同じトランザクションで行うのが仕様（2026-10-26 Kouhei Tajima の判断）。TC-UT_WLD-066 は enterLimitStopped を何もしない差し替えにして、updateSettings だけで limit_stopped になることを期待するので、実施では NG になる見込み</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：GET /world・GET /settings は、現在の世界がないとき find と create を別に行う。同時に2回届くと、2回目の createInitialWorld が ux_worlds_current に当たって 500 になりうる（管理者は1人のため影響は小さい）。TC-UT_WLD-055 は順に2回呼んだときだけを見ている</t>
+          <t>・疑い 2：GET /world・GET /settings は、現在の世界がないとき find と create を別に行う。2回目の createInitialWorld が ux_worlds_current に当たると 500 になりうる。500 は仕様ではない（2026-10-26 Kouhei Tajima の判断）。TC-UT_WLD-067 で同時の2回を見る。ただしハンドラーの find と create は同期の処理で間に await がないため、1つのプロセスの中では割り込まれず、実施では OK になる見込み</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 3：countAgentsByState の active・stopped 以外の state（settingsService.ts:185 の偽）、world_settings がないとき（settingsService.ts:212・270、worldRoutes.ts:119）、楽観の確認で 0 行（settingsService.ts:311）、enterLimitStopped の後に limit_stopped でない（settingsService.ts:333）は、CHECK 制約と同期のトランザクションのため単体テストでは起こせない。分岐の一覧からは外した</t>
+          <t>・確認事項 1：countAgentsByState の active・stopped 以外の state（settingsService.ts:185 の偽）、world_settings がないとき（settingsService.ts:212・270、worldRoutes.ts:119）、楽観の確認で 0 行（settingsService.ts:311）、enterLimitStopped の後に limit_stopped でない（settingsService.ts:333）は、CHECK 制約と同期のトランザクションのため単体テストでは起こせない。分岐の一覧からは外した</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 4：resolveGenerationConfig の既定（config/generation.json を読んでキャッシュする）は、リポジトリのファイルに依存するため単体テストでは見ない。DEV と UT は configureWorldApi か generationConfig の引数で差し替えている</t>
+          <t>・確認事項 2：resolveGenerationConfig の既定（B18-F、config/generation.json を読んでキャッシュする）は、TC-NOUS58_DEV-19 が configureWorldApi で scheduler だけを渡すため、リポジトリの config/generation.json を読んで通る。2回目の呼び出しでキャッシュを使う側（worldRoutes.ts:72 の ??= の偽）は、テストごとに resetWorldApi で消すため単体テストでは見ない</t>
         </is>
       </c>
     </row>
